--- a/process_mining_assignment/process_mining_report_Input.xlsx
+++ b/process_mining_assignment/process_mining_report_Input.xlsx
@@ -420,7 +420,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
@@ -569,7 +569,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>em-6555555556-1</t>
+          <t>Em-6555555556-1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Chu-4208333333-3</t>
+          <t>Ch-4208333333-3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1055,7 +1055,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>co-6751157407-3</t>
+          <t>Co-6751157407-3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Confirm Order</t>
+          <t>Confirm order</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1082,7 +1082,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ern-6895833333-3</t>
+          <t>Em-6895833333-3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AE-4340277778-3</t>
+          <t>Ar-4340277778-3</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Confirm Order</t>
+          <t>Confirm order</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1303,7 +1303,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2012-08-04 12:20</t>
+          <t>2012-08-04 12:32</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>2012-08-04 12:32</t>
+          <t>2012-08-08 09:41</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1357,7 +1357,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>2012-08-08 09:41</t>
+          <t>2012-08-08 10:02</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Re-5888888889-4</t>
+          <t>Ar-5888888889-4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2336,7 +2336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
@@ -2435,7 +2435,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Input: {Confirm order}  →  Output: {Emit invoice, Get shipping address}</t>
+          <t>Input: {Confirm order}  →  Output: {Emit invoice}</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Input: {Emit invoice}  →  Output: {Receive payment}</t>
+          <t>Input: {Confirm order}  →  Output: {Get shipping address}</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Input: {Get shipping address}  →  Output: {Ship product}</t>
+          <t>Input: {Emit invoice}  →  Output: {Receive payment}</t>
         </is>
       </c>
     </row>
@@ -2471,7 +2471,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Input: {Receive payment, Ship product}  →  Output: {Archive order}</t>
+          <t>Input: {Get shipping address}  →  Output: {Ship product}</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Input: {Request raw materials}  →  Output: {Obtain raw materials}</t>
+          <t>Input: {Receive payment}  →  Output: {Archive order}</t>
         </is>
       </c>
     </row>
@@ -2495,7 +2495,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Input: {Check materials availability, Obtain raw materials}  →  Output: {Manufacture product}</t>
+          <t>Input: {Request raw materials}  →  Output: {Obtain raw materials}</t>
         </is>
       </c>
     </row>
@@ -2507,29 +2507,53 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Input: {Manufacture product, Retrieve product from warehouse}  →  Output: {Confirm order}</t>
+          <t>Input: {Ship product}  →  Output: {Archive order}</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>p_start (source)</t>
+          <t>Place p10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>→ ['Check stock availability']</t>
+          <t>Input: {Check materials availability, Obtain raw materials}  →  Output: {Manufacture product}</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>Place p11</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Input: {Manufacture product, Retrieve product from warehouse}  →  Output: {Confirm order}</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>p_start (source)</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>→ ['Check stock availability']</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
           <t>p_end (sink)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>['Archive order'] →</t>
         </is>
@@ -2592,7 +2616,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
